--- a/eda/ket_qua/ket_qua_modelNB_processed.xlsx
+++ b/eda/ket_qua/ket_qua_modelNB_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +546,58 @@
       </c>
       <c r="H4" t="n">
         <v>0.6037735849056604</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7520614954577219</v>
+      </c>
+      <c r="D5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G5" t="n">
+        <v>118</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.7292576419213974</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7520614954577219</v>
+      </c>
+      <c r="D6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E6" t="n">
+        <v>31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>31</v>
+      </c>
+      <c r="G6" t="n">
+        <v>119</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6075949367088608</v>
       </c>
     </row>
   </sheetData>

--- a/eda/ket_qua/ket_qua_modelNB_processed.xlsx
+++ b/eda/ket_qua/ket_qua_modelNB_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,131 +472,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.6875</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7229437229437229</v>
+        <v>0.7248908296943232</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7617051013277429</v>
+        <v>0.7520614954577219</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5844155844155844</v>
+        <v>0.6037735849056604</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.6875</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7229437229437229</v>
+        <v>0.7292576419213974</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7617051013277429</v>
+        <v>0.7520614954577219</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5844155844155844</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7248908296943232</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7520614954577219</v>
-      </c>
-      <c r="D4" t="n">
-        <v>48</v>
-      </c>
-      <c r="E4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F4" t="n">
-        <v>31</v>
-      </c>
-      <c r="G4" t="n">
-        <v>118</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.6037735849056604</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.7248908296943232</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.7520614954577219</v>
-      </c>
-      <c r="D5" t="n">
-        <v>48</v>
-      </c>
-      <c r="E5" t="n">
-        <v>32</v>
-      </c>
-      <c r="F5" t="n">
-        <v>31</v>
-      </c>
-      <c r="G5" t="n">
-        <v>118</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.6037735849056604</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.7292576419213974</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.7520614954577219</v>
-      </c>
-      <c r="D6" t="n">
-        <v>48</v>
-      </c>
-      <c r="E6" t="n">
-        <v>31</v>
-      </c>
-      <c r="F6" t="n">
-        <v>31</v>
-      </c>
-      <c r="G6" t="n">
-        <v>119</v>
-      </c>
-      <c r="H6" t="n">
         <v>0.6075949367088608</v>
       </c>
     </row>
